--- a/www/flightdata/xlsx/eoss-371.xlsx
+++ b/www/flightdata/xlsx/eoss-371.xlsx
@@ -4560,7 +4560,7 @@
         <v>28673.76</v>
       </c>
       <c r="I2">
-        <v>954</v>
+        <v>623</v>
       </c>
       <c r="J2" t="s">
         <v>43</v>
